--- a/Koszty/amortyzacja_26.xlsx
+++ b/Koszty/amortyzacja_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studmsugedupl-my.sharepoint.com/personal/a_mazur_177_studms_ug_edu_pl/Documents/Dokumenty/Praca/P&amp;L/PiL_excel/Koszty/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avistapl-my.sharepoint.com/personal/kp_avistapl_onmicrosoft_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{3FA44F47-5117-4E7C-B58E-6D2DF8B1A6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75FF164D-93B0-4446-A827-B82A5C0F967D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB3E7300-AE04-466D-AECC-42651535BE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9750" yWindow="1830" windowWidth="16755" windowHeight="11670" xr2:uid="{F43583CD-4CA5-4225-8524-8CC9137B419C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{F43583CD-4CA5-4225-8524-8CC9137B419C}"/>
   </bookViews>
   <sheets>
     <sheet name="ST40_FAA2000" sheetId="1" r:id="rId1"/>
@@ -39,53 +39,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={E564A02C-957A-4795-8B22-CCEB947699E8}</author>
-    <author>tc={79A9F2B3-209A-4238-B7B8-CA133F82A235}</author>
-    <author>tc={ACA4AE6B-8C3F-42E6-BEA0-650F3B7E87B5}</author>
-    <author>tc={89259D5E-AEF1-4542-BCD8-2411312CFB71}</author>
-  </authors>
-  <commentList>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{E564A02C-957A-4795-8B22-CCEB947699E8}">
-      <text>
-        <t>[Komentarz podzielony na wątki]
-Używana wersja programu Excel umożliwia odczytanie tego komentarza podzielonego na wątki, jednak wszelkie wprowadzone w nim zmiany zostaną usunięte po otwarciu pliku w nowszej wersji programu Excel. Dowiedz się więcej: https://go.microsoft.com/fwlink/?linkid=870924
-Komentarz:
-    Nr umowny, do zmiany</t>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="1" shapeId="0" xr:uid="{79A9F2B3-209A-4238-B7B8-CA133F82A235}">
-      <text>
-        <t>[Komentarz podzielony na wątki]
-Używana wersja programu Excel umożliwia odczytanie tego komentarza podzielonego na wątki, jednak wszelkie wprowadzone w nim zmiany zostaną usunięte po otwarciu pliku w nowszej wersji programu Excel. Dowiedz się więcej: https://go.microsoft.com/fwlink/?linkid=870924
-Komentarz:
-    Nr umowny, do zmiany</t>
-      </text>
-    </comment>
-    <comment ref="C7" authorId="2" shapeId="0" xr:uid="{ACA4AE6B-8C3F-42E6-BEA0-650F3B7E87B5}">
-      <text>
-        <t>[Komentarz podzielony na wątki]
-Używana wersja programu Excel umożliwia odczytanie tego komentarza podzielonego na wątki, jednak wszelkie wprowadzone w nim zmiany zostaną usunięte po otwarciu pliku w nowszej wersji programu Excel. Dowiedz się więcej: https://go.microsoft.com/fwlink/?linkid=870924
-Komentarz:
-    Nr umowny, do zmiany</t>
-      </text>
-    </comment>
-    <comment ref="C10" authorId="3" shapeId="0" xr:uid="{89259D5E-AEF1-4542-BCD8-2411312CFB71}">
-      <text>
-        <t>[Komentarz podzielony na wątki]
-Używana wersja programu Excel umożliwia odczytanie tego komentarza podzielonego na wątki, jednak wszelkie wprowadzone w nim zmiany zostaną usunięte po otwarciu pliku w nowszej wersji programu Excel. Dowiedz się więcej: https://go.microsoft.com/fwlink/?linkid=870924
-Komentarz:
-    Nr umowny, do zmiany</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="90">
   <si>
     <t>WARTOŚĆ MIESIĘCZNEGO UMORZENIA - AMORTYZACJI 2026</t>
   </si>
@@ -138,49 +93,37 @@
     <t>XII</t>
   </si>
   <si>
-    <t>SN-02</t>
+    <t>FAA 2000</t>
+  </si>
+  <si>
+    <t>XII/19</t>
   </si>
   <si>
     <t>ST-40</t>
   </si>
   <si>
+    <t>IX/19</t>
+  </si>
+  <si>
+    <t>XI/20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IX/20 </t>
+  </si>
+  <si>
+    <t>IX/20</t>
+  </si>
+  <si>
+    <t>MAG.</t>
+  </si>
+  <si>
     <t>V/20</t>
   </si>
   <si>
-    <t>SN-03</t>
+    <t>II/20</t>
   </si>
   <si>
     <t>VIII/20</t>
-  </si>
-  <si>
-    <t>XII/19</t>
-  </si>
-  <si>
-    <t>II/20</t>
-  </si>
-  <si>
-    <t>SN-01</t>
-  </si>
-  <si>
-    <t>MAG.</t>
-  </si>
-  <si>
-    <t>IX/19</t>
-  </si>
-  <si>
-    <t>SN-04</t>
-  </si>
-  <si>
-    <t>FAA 2000</t>
-  </si>
-  <si>
-    <t>XI/20</t>
-  </si>
-  <si>
-    <t>IX/20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IX/20 </t>
   </si>
   <si>
     <t>Lp.</t>
@@ -378,16 +321,7 @@
     <t>Warszawa Centralna</t>
   </si>
   <si>
-    <t xml:space="preserve">od 19.03.2026 </t>
-  </si>
-  <si>
     <t>Warszawa Zachodnia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">od 05.03.2026 </t>
-  </si>
-  <si>
-    <t>work</t>
   </si>
 </sst>
 </file>
@@ -398,7 +332,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _z_ł_-;\-* #,##0.00\ _z_ł_-;_-* &quot;-&quot;??\ _z_ł_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,13 +371,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF1D1C1D"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
@@ -621,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -691,14 +618,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -713,19 +634,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -734,20 +648,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -767,10 +690,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -785,12 +708,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -803,12 +726,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Kaja Peciak" id="{40C2F719-A448-436C-BDC4-D3B2715EDBD9}" userId="S::kp@avistapl.onmicrosoft.com::3f08118e-a98c-47a7-aa81-041e17cd8489" providerId="AD"/>
-</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1126,34 +1043,17 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C3" dT="2026-04-17T18:38:20.45" personId="{40C2F719-A448-436C-BDC4-D3B2715EDBD9}" id="{E564A02C-957A-4795-8B22-CCEB947699E8}">
-    <text>Nr umowny, do zmiany</text>
-  </threadedComment>
-  <threadedComment ref="C4" dT="2026-04-17T18:38:20.45" personId="{40C2F719-A448-436C-BDC4-D3B2715EDBD9}" id="{79A9F2B3-209A-4238-B7B8-CA133F82A235}">
-    <text>Nr umowny, do zmiany</text>
-  </threadedComment>
-  <threadedComment ref="C7" dT="2026-04-17T18:38:20.45" personId="{40C2F719-A448-436C-BDC4-D3B2715EDBD9}" id="{ACA4AE6B-8C3F-42E6-BEA0-650F3B7E87B5}">
-    <text>Nr umowny, do zmiany</text>
-  </threadedComment>
-  <threadedComment ref="C10" dT="2026-04-17T18:38:20.45" personId="{40C2F719-A448-436C-BDC4-D3B2715EDBD9}" id="{89259D5E-AEF1-4542-BCD8-2411312CFB71}">
-    <text>Nr umowny, do zmiany</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1079F13B-D4AE-464C-B286-11E1D5ACF627}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1079F13B-D4AE-464C-B286-11E1D5ACF627}">
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" style="8" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" style="6" customWidth="1"/>
     <col min="7" max="7" width="9.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.42578125" style="5" customWidth="1"/>
     <col min="9" max="14" width="8.85546875" style="5"/>
@@ -1161,27 +1061,27 @@
     <col min="16" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="G1" s="53" t="s">
+    <row r="1" spans="1:18">
+      <c r="G1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="59"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="57"/>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="27" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="23" t="s">
@@ -1190,74 +1090,74 @@
       <c r="D2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" s="45" t="s">
+      <c r="E2" s="26"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="45" t="s">
+      <c r="K2" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="45" t="s">
+      <c r="L2" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="45" t="s">
+      <c r="M2" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="45" t="s">
+      <c r="N2" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="45" t="s">
+      <c r="O2" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="45" t="s">
+      <c r="P2" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="45" t="s">
+      <c r="Q2" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="46" t="s">
+      <c r="R2" s="41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18">
       <c r="A3" s="23">
-        <v>1</v>
-      </c>
-      <c r="B3" s="29">
-        <v>1205</v>
-      </c>
-      <c r="C3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="27">
+        <v>1223</v>
+      </c>
+      <c r="C3" s="23">
+        <v>130036463</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="4">
-        <f>2143.25/2</f>
-        <v>1071.625</v>
+        <v>617.61</v>
       </c>
       <c r="H3" s="4">
-        <f>2143.25/2</f>
-        <v>1071.625</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+        <v>617.61</v>
+      </c>
+      <c r="I3" s="4">
+        <v>617.61</v>
+      </c>
+      <c r="J3" s="4">
+        <v>617.61</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -1267,65 +1167,73 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18">
       <c r="A4" s="23">
-        <v>2</v>
-      </c>
-      <c r="B4" s="29">
-        <v>1211</v>
-      </c>
-      <c r="C4" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="27">
+        <v>1217</v>
+      </c>
+      <c r="C4" s="24">
+        <v>130076353</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="4">
-        <v>1096.25</v>
+        <v>932.27</v>
       </c>
       <c r="H4" s="4">
-        <v>1096.25</v>
-      </c>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+        <v>932.27</v>
+      </c>
+      <c r="I4" s="4">
+        <v>932.27</v>
+      </c>
+      <c r="J4" s="4">
+        <v>932.27</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="23">
-        <v>3</v>
-      </c>
-      <c r="B5" s="29">
-        <v>1212</v>
-      </c>
-      <c r="C5" s="35">
-        <v>130087673</v>
+        <v>19</v>
+      </c>
+      <c r="B5" s="27">
+        <v>1246</v>
+      </c>
+      <c r="C5" s="42">
+        <v>130082537</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="4">
-        <v>1047.8900000000001</v>
+        <v>932.27</v>
       </c>
       <c r="H5" s="4">
-        <v>1047.8900000000001</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+        <v>932.27</v>
+      </c>
+      <c r="I5" s="4">
+        <v>932.27</v>
+      </c>
+      <c r="J5" s="4">
+        <v>932.27</v>
+      </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1335,31 +1243,35 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18">
       <c r="A6" s="23">
-        <v>4</v>
-      </c>
-      <c r="B6" s="29">
-        <v>1213</v>
+        <v>24</v>
+      </c>
+      <c r="B6" s="27">
+        <v>1269</v>
       </c>
       <c r="C6" s="24">
-        <v>130087520</v>
+        <v>130066016</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="4">
-        <v>1093.3699999999999</v>
+        <v>932.27</v>
       </c>
       <c r="H6" s="4">
-        <v>1093.3699999999999</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+        <v>932.27</v>
+      </c>
+      <c r="I6" s="4">
+        <v>932.27</v>
+      </c>
+      <c r="J6" s="4">
+        <v>932.27</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1369,99 +1281,113 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18">
       <c r="A7" s="23">
-        <v>5</v>
-      </c>
-      <c r="B7" s="29">
-        <v>1215</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="25"/>
+        <v>15</v>
+      </c>
+      <c r="B7" s="27">
+        <v>1232</v>
+      </c>
+      <c r="C7" s="8">
+        <v>130087675</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="4">
-        <f>2143.25/2</f>
-        <v>1071.625</v>
+        <v>1041.74</v>
       </c>
       <c r="H7" s="4">
-        <f>2143.25/2</f>
-        <v>1071.625</v>
-      </c>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+        <v>1041.74</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1041.74</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1041.74</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+    </row>
+    <row r="8" spans="1:18" ht="14.45">
       <c r="A8" s="23">
-        <v>6</v>
-      </c>
-      <c r="B8" s="29">
-        <v>1216</v>
-      </c>
-      <c r="C8" s="23">
-        <v>130087676</v>
+        <v>25</v>
+      </c>
+      <c r="B8" s="27">
+        <v>1273</v>
+      </c>
+      <c r="C8" s="24">
+        <v>130066020</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>25</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F8" s="32"/>
       <c r="G8" s="4">
-        <v>1096.25</v>
+        <v>1041.74</v>
       </c>
       <c r="H8" s="4">
-        <v>1096.25</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+        <v>1041.74</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1041.74</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1041.74</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="23">
-        <v>7</v>
-      </c>
-      <c r="B9" s="29">
-        <v>1217</v>
-      </c>
-      <c r="C9" s="24">
-        <v>130076353</v>
+        <v>23</v>
+      </c>
+      <c r="B9" s="27">
+        <v>1255</v>
+      </c>
+      <c r="C9" s="23">
+        <v>130087679</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>24</v>
+      </c>
       <c r="G9" s="4">
-        <v>932.27</v>
+        <v>1041.74</v>
       </c>
       <c r="H9" s="4">
-        <v>932.27</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+        <v>1041.74</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1041.74</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1041.74</v>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1471,21 +1397,21 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18">
       <c r="A10" s="23">
-        <v>9</v>
-      </c>
-      <c r="B10" s="29">
-        <v>1221</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="B10" s="27">
+        <v>1212</v>
+      </c>
+      <c r="C10" s="34">
+        <v>130087673</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="4">
@@ -1494,8 +1420,12 @@
       <c r="H10" s="4">
         <v>1047.8900000000001</v>
       </c>
-      <c r="I10" s="27"/>
-      <c r="J10" s="4"/>
+      <c r="I10" s="4">
+        <v>1047.8900000000001</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1047.8900000000001</v>
+      </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
@@ -1505,31 +1435,35 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18">
       <c r="A11" s="23">
-        <v>10</v>
-      </c>
-      <c r="B11" s="29">
-        <v>1223</v>
+        <v>9</v>
+      </c>
+      <c r="B11" s="27">
+        <v>1221</v>
       </c>
       <c r="C11" s="8">
-        <v>130036463</v>
+        <v>130087523</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="4">
-        <v>617.61</v>
+        <v>1047.8900000000001</v>
       </c>
       <c r="H11" s="4">
-        <v>617.61</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+        <v>1047.8900000000001</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1047.8900000000001</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1047.8900000000001</v>
+      </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1539,24 +1473,24 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18">
       <c r="A12" s="23">
         <v>11</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="27">
         <v>1228</v>
       </c>
       <c r="C12" s="23">
         <v>130087535</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>25</v>
+      <c r="F12" s="25" t="s">
+        <v>24</v>
       </c>
       <c r="G12" s="4">
         <v>1047.8900000000001</v>
@@ -1564,8 +1498,12 @@
       <c r="H12" s="4">
         <v>1047.8900000000001</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
+      <c r="I12" s="4">
+        <v>1047.8900000000001</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1047.8900000000001</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1575,7 +1513,7 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18">
       <c r="A13" s="23">
         <v>12</v>
       </c>
@@ -1586,13 +1524,13 @@
         <v>130087532</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>25</v>
+      <c r="F13" s="25" t="s">
+        <v>24</v>
       </c>
       <c r="G13" s="4">
         <v>1047.8900000000001</v>
@@ -1600,8 +1538,12 @@
       <c r="H13" s="4">
         <v>1047.8900000000001</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="I13" s="4">
+        <v>1047.8900000000001</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1047.8900000000001</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -1611,21 +1553,21 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18">
       <c r="A14" s="23">
         <v>13</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="27">
         <v>1230</v>
       </c>
       <c r="C14" s="23">
         <v>130087672</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="4">
@@ -1634,8 +1576,12 @@
       <c r="H14" s="4">
         <v>1047.8900000000001</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="I14" s="4">
+        <v>1047.8900000000001</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1047.8900000000001</v>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1645,24 +1591,24 @@
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18">
       <c r="A15" s="23">
         <v>14</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="27">
         <v>1231</v>
       </c>
       <c r="C15" s="8">
         <v>130087521</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>25</v>
+      <c r="F15" s="25" t="s">
+        <v>24</v>
       </c>
       <c r="G15" s="4">
         <v>1047.8900000000001</v>
@@ -1670,8 +1616,12 @@
       <c r="H15" s="4">
         <v>1047.8900000000001</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
+      <c r="I15" s="4">
+        <v>1047.8900000000001</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1047.8900000000001</v>
+      </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1681,31 +1631,37 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18">
       <c r="A16" s="23">
-        <v>15</v>
-      </c>
-      <c r="B16" s="29">
-        <v>1232</v>
+        <v>16</v>
+      </c>
+      <c r="B16" s="27">
+        <v>1233</v>
       </c>
       <c r="C16" s="23">
-        <v>130087675</v>
+        <v>130087669</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="1"/>
+      <c r="F16" s="43" t="s">
+        <v>24</v>
+      </c>
       <c r="G16" s="4">
-        <v>1041.74</v>
+        <v>1047.8900000000001</v>
       </c>
       <c r="H16" s="4">
-        <v>1041.74</v>
-      </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+        <v>1047.8900000000001</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1047.8900000000001</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1047.8900000000001</v>
+      </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -1715,33 +1671,35 @@
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18">
       <c r="A17" s="23">
-        <v>16</v>
-      </c>
-      <c r="B17" s="29">
-        <v>1233</v>
-      </c>
-      <c r="C17" s="23">
-        <v>130087669</v>
+        <v>17</v>
+      </c>
+      <c r="B17" s="27">
+        <v>1242</v>
+      </c>
+      <c r="C17" s="34">
+        <v>130087526</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>25</v>
-      </c>
+      <c r="F17" s="9"/>
       <c r="G17" s="4">
         <v>1047.8900000000001</v>
       </c>
       <c r="H17" s="4">
         <v>1047.8900000000001</v>
       </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="I17" s="4">
+        <v>1047.8900000000001</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1047.8900000000001</v>
+      </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -1751,21 +1709,21 @@
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18">
       <c r="A18" s="23">
-        <v>17</v>
-      </c>
-      <c r="B18" s="29">
-        <v>1242</v>
-      </c>
-      <c r="C18" s="38">
-        <v>130087526</v>
+        <v>18</v>
+      </c>
+      <c r="B18" s="27">
+        <v>1245</v>
+      </c>
+      <c r="C18" s="23">
+        <v>130087678</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="4">
@@ -1774,8 +1732,12 @@
       <c r="H18" s="4">
         <v>1047.8900000000001</v>
       </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
+      <c r="I18" s="4">
+        <v>1047.8900000000001</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1047.8900000000001</v>
+      </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -1785,31 +1747,39 @@
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18">
       <c r="A19" s="23">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" s="23">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="C19" s="23">
-        <v>130087678</v>
+        <v>130087675</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="4">
-        <v>1047.8900000000001</v>
+        <f>2136.33/2</f>
+        <v>1068.165</v>
       </c>
       <c r="H19" s="4">
-        <v>1047.8900000000001</v>
-      </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
+        <f>2136.33/2</f>
+        <v>1068.165</v>
+      </c>
+      <c r="I19" s="4">
+        <f t="shared" ref="I19:J20" si="0">2136.33/2</f>
+        <v>1068.165</v>
+      </c>
+      <c r="J19" s="4">
+        <f t="shared" si="0"/>
+        <v>1068.165</v>
+      </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -1819,31 +1789,41 @@
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18">
       <c r="A20" s="23">
+        <v>22</v>
+      </c>
+      <c r="B20" s="23">
+        <v>1253</v>
+      </c>
+      <c r="C20" s="23">
+        <v>130087529</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="23">
-        <v>1246</v>
-      </c>
-      <c r="C20" s="38">
-        <v>130082537</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>18</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>24</v>
+      </c>
       <c r="G20" s="4">
-        <v>932.27</v>
+        <f>2136.33/2</f>
+        <v>1068.165</v>
       </c>
       <c r="H20" s="4">
-        <v>932.27</v>
-      </c>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+        <f>2136.33/2</f>
+        <v>1068.165</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="0"/>
+        <v>1068.165</v>
+      </c>
+      <c r="J20" s="4">
+        <f t="shared" si="0"/>
+        <v>1068.165</v>
+      </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -1853,33 +1833,39 @@
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18">
       <c r="A21" s="23">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B21" s="23">
-        <v>1251</v>
+        <v>1205</v>
       </c>
       <c r="C21" s="23">
-        <v>130066021</v>
+        <v>130087531</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="26" t="s">
         <v>25</v>
       </c>
+      <c r="F21" s="9"/>
       <c r="G21" s="4">
-        <v>1096.25</v>
+        <f>2143.25/2</f>
+        <v>1071.625</v>
       </c>
       <c r="H21" s="4">
-        <v>1096.25</v>
-      </c>
-      <c r="I21" s="27"/>
-      <c r="J21" s="4"/>
+        <f>2143.25/2</f>
+        <v>1071.625</v>
+      </c>
+      <c r="I21" s="4">
+        <f t="shared" ref="I21:J22" si="1">2143.25/2</f>
+        <v>1071.625</v>
+      </c>
+      <c r="J21" s="4">
+        <f t="shared" si="1"/>
+        <v>1071.625</v>
+      </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -1889,71 +1875,77 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18">
       <c r="A22" s="23">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B22" s="23">
-        <v>1252</v>
+        <v>1215</v>
       </c>
       <c r="C22" s="23">
-        <v>130087675</v>
+        <v>130087677</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="23"/>
+      <c r="G22" s="4">
+        <f>2143.25/2</f>
+        <v>1071.625</v>
+      </c>
+      <c r="H22" s="4">
+        <f>2143.25/2</f>
+        <v>1071.625</v>
+      </c>
+      <c r="I22" s="4">
+        <f t="shared" si="1"/>
+        <v>1071.625</v>
+      </c>
+      <c r="J22" s="4">
+        <f t="shared" si="1"/>
+        <v>1071.625</v>
+      </c>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="23">
+        <v>4</v>
+      </c>
+      <c r="B23" s="23">
+        <v>1213</v>
+      </c>
+      <c r="C23" s="24">
+        <v>130087520</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="4">
-        <f>2136.33/2</f>
-        <v>1068.165</v>
-      </c>
-      <c r="H22" s="4">
-        <f>2136.33/2</f>
-        <v>1068.165</v>
-      </c>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" s="23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="23">
-        <v>1253</v>
-      </c>
-      <c r="C23" s="23">
-        <v>130087529</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>18</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>25</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F23" s="9"/>
       <c r="G23" s="4">
-        <f>2136.33/2</f>
-        <v>1068.165</v>
+        <v>1093.3699999999999</v>
       </c>
       <c r="H23" s="4">
-        <f>2136.33/2</f>
-        <v>1068.165</v>
-      </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
+        <v>1093.3699999999999</v>
+      </c>
+      <c r="I23" s="4">
+        <v>1093.3699999999999</v>
+      </c>
+      <c r="J23" s="4">
+        <v>1093.3699999999999</v>
+      </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -1963,67 +1955,75 @@
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18">
       <c r="A24" s="23">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B24" s="23">
-        <v>1255</v>
+        <v>1211</v>
       </c>
       <c r="C24" s="23">
-        <v>130087679</v>
+        <v>130076362</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>25</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F24" s="9"/>
       <c r="G24" s="4">
-        <v>1041.74</v>
+        <v>1096.25</v>
       </c>
       <c r="H24" s="4">
-        <v>1041.74</v>
-      </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+        <v>1096.25</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1096.25</v>
+      </c>
+      <c r="J24" s="4">
+        <v>1096.25</v>
+      </c>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="23">
+        <v>6</v>
+      </c>
+      <c r="B25" s="23">
+        <v>1216</v>
+      </c>
+      <c r="C25" s="23">
+        <v>130087676</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="23">
-        <v>1269</v>
-      </c>
-      <c r="C25" s="24">
-        <v>130066016</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="9"/>
       <c r="G25" s="4">
-        <v>932.27</v>
+        <v>1096.25</v>
       </c>
       <c r="H25" s="4">
-        <v>932.27</v>
-      </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
+        <v>1096.25</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1096.25</v>
+      </c>
+      <c r="J25" s="4">
+        <v>1096.25</v>
+      </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2033,162 +2033,168 @@
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
     </row>
-    <row r="26" spans="1:18" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="13.9" customHeight="1">
       <c r="A26" s="23">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B26" s="23">
-        <v>1273</v>
-      </c>
-      <c r="C26" s="24">
-        <v>130066020</v>
+        <v>1251</v>
+      </c>
+      <c r="C26" s="23">
+        <v>130066021</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="36"/>
+        <v>27</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>24</v>
+      </c>
       <c r="G26" s="4">
-        <v>1041.74</v>
+        <v>1096.25</v>
       </c>
       <c r="H26" s="4">
-        <v>1041.74</v>
-      </c>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
+        <v>1096.25</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1096.25</v>
+      </c>
+      <c r="J26" s="4">
+        <v>1096.25</v>
+      </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
-      <c r="Q26" s="37"/>
-      <c r="R26" s="37"/>
-    </row>
-    <row r="27" spans="1:18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" ht="14.45">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="42">
-        <f t="shared" ref="G27:R27" si="0">SUM(G3:G26)</f>
-        <v>24632.350000000002</v>
-      </c>
-      <c r="H27" s="42">
-        <f t="shared" si="0"/>
-        <v>24632.350000000002</v>
-      </c>
-      <c r="I27" s="42">
-        <f t="shared" si="0"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="37">
+        <f t="shared" ref="G27:R27" si="2">SUM(G3:G26)</f>
+        <v>24632.349999999995</v>
+      </c>
+      <c r="H27" s="37">
+        <f t="shared" si="2"/>
+        <v>24632.349999999995</v>
+      </c>
+      <c r="I27" s="37">
+        <f t="shared" si="2"/>
+        <v>24632.349999999995</v>
+      </c>
+      <c r="J27" s="37">
+        <f t="shared" si="2"/>
+        <v>24632.349999999995</v>
+      </c>
+      <c r="K27" s="37">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J27" s="42">
-        <f t="shared" si="0"/>
+      <c r="L27" s="37">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K27" s="42">
-        <f t="shared" si="0"/>
+      <c r="M27" s="37">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="42">
-        <f t="shared" si="0"/>
+      <c r="N27" s="37">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M27" s="42">
-        <f t="shared" si="0"/>
+      <c r="O27" s="37">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N27" s="42">
-        <f t="shared" si="0"/>
+      <c r="P27" s="37">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O27" s="42">
-        <f t="shared" si="0"/>
+      <c r="Q27" s="37">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P27" s="42">
-        <f t="shared" si="0"/>
+      <c r="R27" s="37">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="42">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R27" s="42">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:18" ht="14.45">
       <c r="B28"/>
     </row>
-    <row r="29" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="14.45">
       <c r="B29"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:R2" xr:uid="{1079F13B-D4AE-464C-B286-11E1D5ACF627}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:R32">
-      <sortCondition ref="B2"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:R27">
+      <sortCondition ref="G2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="G1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{829BDEAE-E67D-4606-BE2F-DBD37344F7AC}">
   <dimension ref="A1:Q48"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="11.45"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="8"/>
     <col min="2" max="2" width="11" style="8" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" style="8" customWidth="1"/>
     <col min="4" max="4" width="8.85546875" style="7"/>
-    <col min="5" max="5" width="30.42578125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" style="7" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="8" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" style="8"/>
     <col min="11" max="15" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="8.85546875" style="8"/>
     <col min="18" max="16384" width="8.85546875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A1" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="53" t="s">
+    <row r="1" spans="1:17" ht="12">
+      <c r="A1" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="50"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+    </row>
+    <row r="2" spans="1:17" ht="12">
+      <c r="A2" s="48"/>
       <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
@@ -2196,56 +2202,56 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="45" t="s">
+      <c r="K2" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="45" t="s">
+      <c r="L2" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="45" t="s">
+      <c r="M2" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="45" t="s">
+      <c r="N2" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="45" t="s">
+      <c r="O2" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="45" t="s">
+      <c r="P2" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="46" t="s">
+      <c r="Q2" s="41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17">
       <c r="A3" s="9"/>
-      <c r="B3" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
+      <c r="B3" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
@@ -2259,12 +2265,12 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="11"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="57"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
+    <row r="4" spans="1:17">
+      <c r="A4" s="55"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
@@ -2278,7 +2284,7 @@
       <c r="P4" s="13"/>
       <c r="Q4" s="14"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" s="9">
         <v>1</v>
       </c>
@@ -2289,10 +2295,10 @@
         <v>1101</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F5" s="18">
         <v>862.79</v>
@@ -2300,8 +2306,12 @@
       <c r="G5" s="18">
         <v>862.79</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
+      <c r="H5" s="44">
+        <v>862.79</v>
+      </c>
+      <c r="I5" s="44">
+        <v>862.79</v>
+      </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
       <c r="L5" s="18"/>
@@ -2310,7 +2320,7 @@
       <c r="O5" s="18"/>
       <c r="Q5" s="18"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17">
       <c r="A6" s="9">
         <v>2</v>
       </c>
@@ -2321,10 +2331,10 @@
         <v>1102</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F6" s="18">
         <v>862.79</v>
@@ -2332,8 +2342,12 @@
       <c r="G6" s="18">
         <v>862.79</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
+      <c r="H6" s="44">
+        <v>862.79</v>
+      </c>
+      <c r="I6" s="44">
+        <v>862.79</v>
+      </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
@@ -2342,7 +2356,7 @@
       <c r="O6" s="18"/>
       <c r="Q6" s="18"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17">
       <c r="A7" s="9">
         <v>3</v>
       </c>
@@ -2353,10 +2367,10 @@
         <v>1103</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F7" s="18">
         <v>862.79</v>
@@ -2364,8 +2378,12 @@
       <c r="G7" s="18">
         <v>862.79</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
+      <c r="H7" s="44">
+        <v>862.79</v>
+      </c>
+      <c r="I7" s="44">
+        <v>862.79</v>
+      </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
@@ -2374,7 +2392,7 @@
       <c r="O7" s="18"/>
       <c r="Q7" s="18"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17">
       <c r="A8" s="9">
         <v>4</v>
       </c>
@@ -2385,10 +2403,10 @@
         <v>1104</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="F8" s="18">
         <v>862.79</v>
@@ -2396,8 +2414,12 @@
       <c r="G8" s="18">
         <v>862.79</v>
       </c>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
+      <c r="H8" s="44">
+        <v>862.79</v>
+      </c>
+      <c r="I8" s="44">
+        <v>862.79</v>
+      </c>
       <c r="J8" s="18"/>
       <c r="K8" s="18"/>
       <c r="L8" s="18"/>
@@ -2406,7 +2428,7 @@
       <c r="O8" s="18"/>
       <c r="Q8" s="18"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17">
       <c r="A9" s="9">
         <v>5</v>
       </c>
@@ -2417,10 +2439,10 @@
         <v>1105</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F9" s="18">
         <v>862.79</v>
@@ -2428,8 +2450,12 @@
       <c r="G9" s="18">
         <v>862.79</v>
       </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
+      <c r="H9" s="44">
+        <v>862.79</v>
+      </c>
+      <c r="I9" s="44">
+        <v>862.79</v>
+      </c>
       <c r="J9" s="18"/>
       <c r="K9" s="18"/>
       <c r="L9" s="18"/>
@@ -2438,7 +2464,7 @@
       <c r="O9" s="18"/>
       <c r="Q9" s="18"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17">
       <c r="A10" s="9">
         <v>6</v>
       </c>
@@ -2449,10 +2475,10 @@
         <v>1106</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F10" s="18">
         <v>862.79</v>
@@ -2460,8 +2486,12 @@
       <c r="G10" s="18">
         <v>862.79</v>
       </c>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="H10" s="44">
+        <v>862.79</v>
+      </c>
+      <c r="I10" s="44">
+        <v>862.79</v>
+      </c>
       <c r="J10" s="18"/>
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
@@ -2470,7 +2500,7 @@
       <c r="O10" s="18"/>
       <c r="Q10" s="18"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17">
       <c r="A11" s="9">
         <v>7</v>
       </c>
@@ -2481,10 +2511,10 @@
         <v>1107</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F11" s="18">
         <v>862.79</v>
@@ -2492,8 +2522,12 @@
       <c r="G11" s="18">
         <v>862.79</v>
       </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
+      <c r="H11" s="44">
+        <v>862.79</v>
+      </c>
+      <c r="I11" s="44">
+        <v>862.79</v>
+      </c>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
       <c r="L11" s="18"/>
@@ -2502,7 +2536,7 @@
       <c r="O11" s="18"/>
       <c r="Q11" s="18"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17">
       <c r="A12" s="9">
         <v>8</v>
       </c>
@@ -2513,10 +2547,10 @@
         <v>1108</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F12" s="18">
         <v>862.79</v>
@@ -2524,8 +2558,12 @@
       <c r="G12" s="18">
         <v>862.79</v>
       </c>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
+      <c r="H12" s="44">
+        <v>862.79</v>
+      </c>
+      <c r="I12" s="44">
+        <v>862.79</v>
+      </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
@@ -2534,7 +2572,7 @@
       <c r="O12" s="18"/>
       <c r="Q12" s="18"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17">
       <c r="A13" s="9">
         <v>9</v>
       </c>
@@ -2545,10 +2583,10 @@
         <v>1109</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F13" s="18">
         <v>862.79</v>
@@ -2556,8 +2594,12 @@
       <c r="G13" s="18">
         <v>862.79</v>
       </c>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
+      <c r="H13" s="44">
+        <v>862.79</v>
+      </c>
+      <c r="I13" s="44">
+        <v>862.79</v>
+      </c>
       <c r="J13" s="18"/>
       <c r="K13" s="18"/>
       <c r="L13" s="18"/>
@@ -2566,7 +2608,7 @@
       <c r="O13" s="18"/>
       <c r="Q13" s="18"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17">
       <c r="A14" s="9">
         <v>10</v>
       </c>
@@ -2577,10 +2619,10 @@
         <v>1110</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F14" s="18">
         <v>862.8</v>
@@ -2588,8 +2630,12 @@
       <c r="G14" s="18">
         <v>862.8</v>
       </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
+      <c r="H14" s="18">
+        <v>862.8</v>
+      </c>
+      <c r="I14" s="18">
+        <v>862.8</v>
+      </c>
       <c r="J14" s="18"/>
       <c r="K14" s="18"/>
       <c r="L14" s="18"/>
@@ -2598,7 +2644,7 @@
       <c r="O14" s="18"/>
       <c r="Q14" s="18"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17">
       <c r="A15" s="9">
         <v>11</v>
       </c>
@@ -2606,13 +2652,13 @@
         <v>1111</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F15" s="18">
         <v>767.95</v>
@@ -2620,8 +2666,12 @@
       <c r="G15" s="18">
         <v>767.95</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
+      <c r="H15" s="18">
+        <v>767.95</v>
+      </c>
+      <c r="I15" s="18">
+        <v>767.95</v>
+      </c>
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
@@ -2630,7 +2680,7 @@
       <c r="O15" s="18"/>
       <c r="Q15" s="18"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17">
       <c r="A16" s="9">
         <v>12</v>
       </c>
@@ -2638,13 +2688,13 @@
         <v>1112</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F16" s="18">
         <v>789.5</v>
@@ -2652,8 +2702,12 @@
       <c r="G16" s="18">
         <v>789.5</v>
       </c>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
+      <c r="H16" s="18">
+        <v>789.5</v>
+      </c>
+      <c r="I16" s="18">
+        <v>789.5</v>
+      </c>
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
@@ -2662,7 +2716,7 @@
       <c r="O16" s="18"/>
       <c r="Q16" s="18"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17">
       <c r="A17" s="9">
         <v>13</v>
       </c>
@@ -2671,19 +2725,23 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="F17" s="18">
         <v>789.5</v>
       </c>
       <c r="G17" s="18">
         <v>789.5</v>
       </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
+      <c r="H17" s="18">
+        <v>789.5</v>
+      </c>
+      <c r="I17" s="18">
+        <v>789.5</v>
+      </c>
       <c r="J17" s="18"/>
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
@@ -2692,7 +2750,7 @@
       <c r="O17" s="18"/>
       <c r="Q17" s="18"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17">
       <c r="A18" s="9">
         <v>14</v>
       </c>
@@ -2701,10 +2759,10 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F18" s="18">
         <v>789.5</v>
@@ -2712,8 +2770,12 @@
       <c r="G18" s="18">
         <v>789.5</v>
       </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
+      <c r="H18" s="18">
+        <v>789.5</v>
+      </c>
+      <c r="I18" s="18">
+        <v>789.5</v>
+      </c>
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
@@ -2722,7 +2784,7 @@
       <c r="O18" s="18"/>
       <c r="Q18" s="18"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17">
       <c r="A19" s="9">
         <v>15</v>
       </c>
@@ -2731,10 +2793,10 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F19" s="18">
         <v>789.5</v>
@@ -2742,8 +2804,12 @@
       <c r="G19" s="18">
         <v>789.5</v>
       </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
+      <c r="H19" s="18">
+        <v>789.5</v>
+      </c>
+      <c r="I19" s="18">
+        <v>789.5</v>
+      </c>
       <c r="J19" s="18"/>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
@@ -2752,7 +2818,7 @@
       <c r="O19" s="18"/>
       <c r="Q19" s="18"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17">
       <c r="A20" s="9">
         <v>16</v>
       </c>
@@ -2760,13 +2826,13 @@
         <v>1116</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F20" s="18">
         <v>789.5</v>
@@ -2774,8 +2840,12 @@
       <c r="G20" s="18">
         <v>789.5</v>
       </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
+      <c r="H20" s="18">
+        <v>789.5</v>
+      </c>
+      <c r="I20" s="18">
+        <v>789.5</v>
+      </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
       <c r="L20" s="18"/>
@@ -2784,7 +2854,7 @@
       <c r="O20" s="18"/>
       <c r="Q20" s="18"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17">
       <c r="A21" s="9">
         <v>17</v>
       </c>
@@ -2793,10 +2863,10 @@
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F21" s="18">
         <v>789.5</v>
@@ -2804,8 +2874,12 @@
       <c r="G21" s="18">
         <v>789.5</v>
       </c>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
+      <c r="H21" s="18">
+        <v>789.5</v>
+      </c>
+      <c r="I21" s="18">
+        <v>789.5</v>
+      </c>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
       <c r="L21" s="18"/>
@@ -2814,7 +2888,7 @@
       <c r="O21" s="18"/>
       <c r="Q21" s="18"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17">
       <c r="A22" s="9">
         <v>18</v>
       </c>
@@ -2822,13 +2896,13 @@
         <v>1122</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F22" s="18">
         <v>789.5</v>
@@ -2836,8 +2910,12 @@
       <c r="G22" s="18">
         <v>789.5</v>
       </c>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
+      <c r="H22" s="18">
+        <v>789.5</v>
+      </c>
+      <c r="I22" s="18">
+        <v>789.5</v>
+      </c>
       <c r="J22" s="18"/>
       <c r="K22" s="18"/>
       <c r="L22" s="18"/>
@@ -2846,7 +2924,7 @@
       <c r="O22" s="18"/>
       <c r="Q22" s="18"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17">
       <c r="A23" s="9">
         <v>19</v>
       </c>
@@ -2854,10 +2932,10 @@
         <v>1123</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="18">
@@ -2866,8 +2944,12 @@
       <c r="G23" s="18">
         <v>789.5</v>
       </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
+      <c r="H23" s="18">
+        <v>789.5</v>
+      </c>
+      <c r="I23" s="18">
+        <v>789.5</v>
+      </c>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
       <c r="L23" s="18"/>
@@ -2876,7 +2958,7 @@
       <c r="O23" s="18"/>
       <c r="Q23" s="18"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17">
       <c r="A24" s="9">
         <v>20</v>
       </c>
@@ -2884,10 +2966,10 @@
         <v>1124</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F24" s="18">
         <v>789.5</v>
@@ -2895,8 +2977,12 @@
       <c r="G24" s="18">
         <v>789.5</v>
       </c>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
+      <c r="H24" s="18">
+        <v>789.5</v>
+      </c>
+      <c r="I24" s="18">
+        <v>789.5</v>
+      </c>
       <c r="J24" s="18"/>
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
@@ -2905,7 +2991,7 @@
       <c r="O24" s="18"/>
       <c r="Q24" s="18"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17">
       <c r="A25" s="9">
         <v>21</v>
       </c>
@@ -2913,13 +2999,13 @@
         <v>1118</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="31" t="s">
-        <v>66</v>
+        <v>61</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>62</v>
       </c>
       <c r="F25" s="18">
         <v>789.5</v>
@@ -2927,8 +3013,12 @@
       <c r="G25" s="18">
         <v>789.5</v>
       </c>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
+      <c r="H25" s="18">
+        <v>789.5</v>
+      </c>
+      <c r="I25" s="18">
+        <v>789.5</v>
+      </c>
       <c r="J25" s="18"/>
       <c r="K25" s="18"/>
       <c r="L25" s="18"/>
@@ -2937,7 +3027,7 @@
       <c r="O25" s="18"/>
       <c r="Q25" s="18"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17">
       <c r="A26" s="9">
         <v>22</v>
       </c>
@@ -2945,10 +3035,10 @@
         <v>1119</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F26" s="19">
         <v>789.5</v>
@@ -2956,8 +3046,12 @@
       <c r="G26" s="19">
         <v>789.5</v>
       </c>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
+      <c r="H26" s="18">
+        <v>789.5</v>
+      </c>
+      <c r="I26" s="18">
+        <v>789.5</v>
+      </c>
       <c r="J26" s="19"/>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
@@ -2966,7 +3060,7 @@
       <c r="O26" s="19"/>
       <c r="Q26" s="18"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17">
       <c r="A27" s="9">
         <v>23</v>
       </c>
@@ -2975,10 +3069,10 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="16" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F27" s="19">
         <v>810.61</v>
@@ -2986,8 +3080,12 @@
       <c r="G27" s="19">
         <v>810.61</v>
       </c>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
+      <c r="H27" s="19">
+        <v>810.61</v>
+      </c>
+      <c r="I27" s="19">
+        <v>810.61</v>
+      </c>
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
       <c r="L27" s="19"/>
@@ -2996,7 +3094,7 @@
       <c r="O27" s="19"/>
       <c r="Q27" s="19"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17">
       <c r="A28" s="9">
         <v>24</v>
       </c>
@@ -3005,10 +3103,10 @@
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F28" s="19">
         <v>810.61</v>
@@ -3016,8 +3114,12 @@
       <c r="G28" s="19">
         <v>810.61</v>
       </c>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
+      <c r="H28" s="19">
+        <v>810.61</v>
+      </c>
+      <c r="I28" s="19">
+        <v>810.61</v>
+      </c>
       <c r="J28" s="19"/>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
@@ -3026,7 +3128,7 @@
       <c r="O28" s="19"/>
       <c r="Q28" s="19"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17">
       <c r="A29" s="9">
         <v>25</v>
       </c>
@@ -3035,10 +3137,10 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F29" s="19">
         <v>801.73</v>
@@ -3046,8 +3148,12 @@
       <c r="G29" s="19">
         <v>801.73</v>
       </c>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
+      <c r="H29" s="19">
+        <v>801.73</v>
+      </c>
+      <c r="I29" s="19">
+        <v>801.73</v>
+      </c>
       <c r="J29" s="19"/>
       <c r="K29" s="19"/>
       <c r="L29" s="19"/>
@@ -3056,7 +3162,7 @@
       <c r="O29" s="19"/>
       <c r="Q29" s="20"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17">
       <c r="A30" s="9">
         <v>26</v>
       </c>
@@ -3065,21 +3171,27 @@
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F30" s="20">
-        <f>1606.85/2</f>
+        <f t="shared" ref="F30:I31" si="0">1606.85/2</f>
         <v>803.42499999999995</v>
       </c>
       <c r="G30" s="20">
-        <f>1606.85/2</f>
+        <f t="shared" si="0"/>
         <v>803.42499999999995</v>
       </c>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
+      <c r="H30" s="19">
+        <f t="shared" si="0"/>
+        <v>803.42499999999995</v>
+      </c>
+      <c r="I30" s="19">
+        <f t="shared" si="0"/>
+        <v>803.42499999999995</v>
+      </c>
       <c r="J30" s="19"/>
       <c r="K30" s="19"/>
       <c r="L30" s="19"/>
@@ -3088,7 +3200,7 @@
       <c r="O30" s="19"/>
       <c r="Q30" s="20"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17">
       <c r="A31" s="9">
         <v>27</v>
       </c>
@@ -3097,21 +3209,27 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F31" s="20">
-        <f>1606.85/2</f>
+        <f t="shared" si="0"/>
         <v>803.42499999999995</v>
       </c>
       <c r="G31" s="20">
-        <f>1606.85/2</f>
+        <f t="shared" si="0"/>
         <v>803.42499999999995</v>
       </c>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
+      <c r="H31" s="19">
+        <f t="shared" si="0"/>
+        <v>803.42499999999995</v>
+      </c>
+      <c r="I31" s="19">
+        <f t="shared" si="0"/>
+        <v>803.42499999999995</v>
+      </c>
       <c r="J31" s="19"/>
       <c r="K31" s="19"/>
       <c r="L31" s="19"/>
@@ -3120,7 +3238,7 @@
       <c r="O31" s="19"/>
       <c r="Q31" s="20"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17">
       <c r="A32" s="9">
         <v>28</v>
       </c>
@@ -3129,10 +3247,10 @@
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F32" s="19">
         <v>788.44</v>
@@ -3140,8 +3258,12 @@
       <c r="G32" s="19">
         <v>788.44</v>
       </c>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
+      <c r="H32" s="19">
+        <v>788.44</v>
+      </c>
+      <c r="I32" s="19">
+        <v>788.44</v>
+      </c>
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
@@ -3150,7 +3272,7 @@
       <c r="O32" s="19"/>
       <c r="Q32" s="20"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17">
       <c r="A33" s="9">
         <v>29</v>
       </c>
@@ -3159,10 +3281,10 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F33" s="19">
         <v>788.44</v>
@@ -3170,8 +3292,12 @@
       <c r="G33" s="19">
         <v>788.44</v>
       </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
+      <c r="H33" s="19">
+        <v>788.44</v>
+      </c>
+      <c r="I33" s="19">
+        <v>788.44</v>
+      </c>
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
       <c r="L33" s="19"/>
@@ -3180,7 +3306,7 @@
       <c r="O33" s="19"/>
       <c r="Q33" s="20"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17">
       <c r="A34" s="9">
         <v>30</v>
       </c>
@@ -3189,10 +3315,10 @@
       </c>
       <c r="C34" s="15"/>
       <c r="D34" s="16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F34" s="19">
         <v>788.44</v>
@@ -3200,8 +3326,12 @@
       <c r="G34" s="19">
         <v>788.44</v>
       </c>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
+      <c r="H34" s="19">
+        <v>788.44</v>
+      </c>
+      <c r="I34" s="19">
+        <v>788.44</v>
+      </c>
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
       <c r="L34" s="19"/>
@@ -3210,7 +3340,7 @@
       <c r="O34" s="19"/>
       <c r="Q34" s="20"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17">
       <c r="A35" s="9">
         <v>31</v>
       </c>
@@ -3219,10 +3349,10 @@
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F35" s="19">
         <v>788.44</v>
@@ -3230,8 +3360,12 @@
       <c r="G35" s="19">
         <v>788.44</v>
       </c>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
+      <c r="H35" s="19">
+        <v>788.44</v>
+      </c>
+      <c r="I35" s="19">
+        <v>788.44</v>
+      </c>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
       <c r="L35" s="19"/>
@@ -3240,7 +3374,7 @@
       <c r="O35" s="19"/>
       <c r="Q35" s="20"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17">
       <c r="A36" s="9">
         <v>32</v>
       </c>
@@ -3249,10 +3383,10 @@
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F36" s="19">
         <v>788.44</v>
@@ -3260,8 +3394,12 @@
       <c r="G36" s="19">
         <v>788.44</v>
       </c>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
+      <c r="H36" s="19">
+        <v>788.44</v>
+      </c>
+      <c r="I36" s="19">
+        <v>788.44</v>
+      </c>
       <c r="J36" s="19"/>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
@@ -3270,7 +3408,7 @@
       <c r="O36" s="19"/>
       <c r="Q36" s="20"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17">
       <c r="A37" s="9">
         <v>33</v>
       </c>
@@ -3279,10 +3417,10 @@
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="16" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F37" s="19">
         <v>788.44</v>
@@ -3290,8 +3428,12 @@
       <c r="G37" s="19">
         <v>788.44</v>
       </c>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
+      <c r="H37" s="19">
+        <v>788.44</v>
+      </c>
+      <c r="I37" s="19">
+        <v>788.44</v>
+      </c>
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
       <c r="L37" s="19"/>
@@ -3300,7 +3442,7 @@
       <c r="O37" s="19"/>
       <c r="Q37" s="20"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17">
       <c r="A38" s="9">
         <v>34</v>
       </c>
@@ -3309,10 +3451,10 @@
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F38" s="19">
         <v>788.44</v>
@@ -3320,8 +3462,12 @@
       <c r="G38" s="19">
         <v>788.44</v>
       </c>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
+      <c r="H38" s="19">
+        <v>788.44</v>
+      </c>
+      <c r="I38" s="19">
+        <v>788.44</v>
+      </c>
       <c r="J38" s="19"/>
       <c r="K38" s="19"/>
       <c r="L38" s="19"/>
@@ -3330,7 +3476,7 @@
       <c r="O38" s="19"/>
       <c r="Q38" s="20"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17">
       <c r="A39" s="9">
         <v>35</v>
       </c>
@@ -3339,10 +3485,10 @@
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F39" s="19">
         <v>803.42</v>
@@ -3350,8 +3496,12 @@
       <c r="G39" s="19">
         <v>803.42</v>
       </c>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
+      <c r="H39" s="19">
+        <v>803.42</v>
+      </c>
+      <c r="I39" s="19">
+        <v>803.42</v>
+      </c>
       <c r="J39" s="19"/>
       <c r="K39" s="19"/>
       <c r="L39" s="19"/>
@@ -3360,7 +3510,7 @@
       <c r="O39" s="19"/>
       <c r="Q39" s="20"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17">
       <c r="A40" s="9">
         <v>36</v>
       </c>
@@ -3369,10 +3519,10 @@
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="16" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F40" s="20">
         <v>788.44</v>
@@ -3380,8 +3530,12 @@
       <c r="G40" s="20">
         <v>788.44</v>
       </c>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
+      <c r="H40" s="20">
+        <v>788.44</v>
+      </c>
+      <c r="I40" s="20">
+        <v>788.44</v>
+      </c>
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
       <c r="L40" s="19"/>
@@ -3390,7 +3544,7 @@
       <c r="O40" s="19"/>
       <c r="Q40" s="20"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17">
       <c r="A41" s="9">
         <v>37</v>
       </c>
@@ -3399,10 +3553,10 @@
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F41" s="20">
         <v>805.09</v>
@@ -3410,8 +3564,12 @@
       <c r="G41" s="20">
         <v>805.09</v>
       </c>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
+      <c r="H41" s="20">
+        <v>805.09</v>
+      </c>
+      <c r="I41" s="20">
+        <v>805.09</v>
+      </c>
       <c r="J41" s="19"/>
       <c r="K41" s="19"/>
       <c r="L41" s="19"/>
@@ -3420,7 +3578,7 @@
       <c r="O41" s="19"/>
       <c r="Q41" s="20"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17">
       <c r="A42" s="9">
         <v>38</v>
       </c>
@@ -3429,10 +3587,10 @@
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="16" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F42" s="20">
         <v>805.09</v>
@@ -3440,8 +3598,12 @@
       <c r="G42" s="20">
         <v>805.09</v>
       </c>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
+      <c r="H42" s="20">
+        <v>805.09</v>
+      </c>
+      <c r="I42" s="20">
+        <v>805.09</v>
+      </c>
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
       <c r="L42" s="19"/>
@@ -3450,7 +3612,7 @@
       <c r="O42" s="19"/>
       <c r="Q42" s="20"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17">
       <c r="A43" s="9">
         <v>39</v>
       </c>
@@ -3458,22 +3620,24 @@
         <v>1139</v>
       </c>
       <c r="C43" s="15"/>
-      <c r="D43" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E43" s="32" t="s">
-        <v>92</v>
+      <c r="D43" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>88</v>
       </c>
       <c r="F43" s="20">
         <v>0</v>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="31">
         <v>0</v>
       </c>
-      <c r="H43" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="I43" s="18"/>
+      <c r="H43" s="31">
+        <v>0</v>
+      </c>
+      <c r="I43" s="20">
+        <v>805.09</v>
+      </c>
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
       <c r="L43" s="19"/>
@@ -3482,7 +3646,7 @@
       <c r="O43" s="19"/>
       <c r="Q43" s="20"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17">
       <c r="A44" s="9">
         <v>40</v>
       </c>
@@ -3490,20 +3654,24 @@
         <v>1140</v>
       </c>
       <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="32" t="s">
-        <v>92</v>
+      <c r="D44" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>88</v>
       </c>
       <c r="F44" s="20">
         <v>0</v>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="31">
         <v>0</v>
       </c>
-      <c r="H44" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="I44" s="18"/>
+      <c r="H44" s="31">
+        <v>0</v>
+      </c>
+      <c r="I44" s="19">
+        <v>788.44</v>
+      </c>
       <c r="J44" s="19"/>
       <c r="K44" s="19"/>
       <c r="L44" s="19"/>
@@ -3512,7 +3680,7 @@
       <c r="O44" s="19"/>
       <c r="Q44" s="20"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17">
       <c r="A45" s="9">
         <v>41</v>
       </c>
@@ -3520,20 +3688,24 @@
         <v>1141</v>
       </c>
       <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="32" t="s">
-        <v>94</v>
+      <c r="D45" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F45" s="20">
         <v>0</v>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="31">
         <v>0</v>
       </c>
-      <c r="H45" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="I45" s="18"/>
+      <c r="H45" s="31">
+        <v>0</v>
+      </c>
+      <c r="I45" s="19">
+        <v>788.44</v>
+      </c>
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
       <c r="L45" s="19"/>
@@ -3542,56 +3714,56 @@
       <c r="O45" s="19"/>
       <c r="Q45" s="20"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A46" s="47"/>
-      <c r="B46" s="48"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="43">
+    <row r="46" spans="1:17" ht="12">
+      <c r="A46" s="45"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="38">
         <f>SUM(F5:F45)</f>
         <v>30831.279999999988</v>
       </c>
-      <c r="G46" s="43">
+      <c r="G46" s="38">
         <f>SUM(G4:G45)</f>
         <v>30831.279999999988</v>
       </c>
-      <c r="H46" s="43">
+      <c r="H46" s="38">
         <f>SUM(H4:H32)</f>
-        <v>0</v>
-      </c>
-      <c r="I46" s="44">
+        <v>22898.6</v>
+      </c>
+      <c r="I46" s="39">
         <f>SUM(I5:I32)</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="44">
+        <v>22898.6</v>
+      </c>
+      <c r="J46" s="39">
         <f>SUM(J4:J35)</f>
         <v>0</v>
       </c>
-      <c r="K46" s="43">
+      <c r="K46" s="38">
         <f>SUM(K5:K36)</f>
         <v>0</v>
       </c>
-      <c r="L46" s="43">
+      <c r="L46" s="38">
         <f>SUM(L4:L39)</f>
         <v>0</v>
       </c>
-      <c r="M46" s="43">
+      <c r="M46" s="38">
         <f>SUM(M5:M39)</f>
         <v>0</v>
       </c>
-      <c r="N46" s="43">
+      <c r="N46" s="38">
         <f>SUM(N5:N39)</f>
         <v>0</v>
       </c>
-      <c r="O46" s="43">
+      <c r="O46" s="38">
         <f>SUM(O5:O39)</f>
         <v>0</v>
       </c>
-      <c r="P46" s="44"/>
-      <c r="Q46" s="43"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P46" s="39"/>
+      <c r="Q46" s="38"/>
+    </row>
+    <row r="48" spans="1:17">
       <c r="G48" s="21"/>
     </row>
   </sheetData>
